--- a/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
+++ b/Configs/GameConfig/Datas/cell/#BehaviorArchetype-行为原型.xlsx
@@ -2364,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2391,16 +2391,16 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
